--- a/Motor_Selection/Motor Selection.xlsx
+++ b/Motor_Selection/Motor Selection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johnn\MQP\MQP\Motor_Selection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A61D1F1-C834-47B2-8E23-84A64AB88B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABCD90D-F306-44A9-8FDF-EF7AD692594E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{561663A1-5EF6-44DB-8CFA-D0AE34553674}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>GF 7042</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>Efficiency (g/W)</t>
+  </si>
+  <si>
+    <t>Current Mass (g)</t>
+  </si>
+  <si>
+    <t>Per Motor</t>
   </si>
 </sst>
 </file>
@@ -657,7 +663,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2281,6 +2286,652 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Current Vs Throttle</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>HQ 70403</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.71</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.83</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.29</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.64</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36.729999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45.11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$3:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>353.46</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>478.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>596.38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>758.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>947.57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1131.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1290.19</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1585.74</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1865.32</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2210.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2360.61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A223-49BE-B494-9444FB9231E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>GF 7042</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$3:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.62</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.86</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.52</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32.06</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>41.26</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$3:$H$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>319.66000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>433.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>552.09</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>697.52</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>836.04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>988.93</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1196.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1474.19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1783.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1969.91</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2116.5500000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A223-49BE-B494-9444FB9231E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="218500144"/>
+        <c:axId val="99305584"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="218500144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Current</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="99305584"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="99305584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Thrust (g)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="218500144"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2401,6 +3052,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3434,6 +4125,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4027,16 +5234,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4058,6 +5265,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52A5F8EF-22D5-4F20-AA5F-5F04A7E0277F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4383,7 +5628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC6260D-C31C-4D24-87FD-B0D28DF64C21}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -4897,6 +6142,27 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f>A18/4</f>
+        <v>560.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4905,6 +6171,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007E97EDF357961C4C88A01A167EC7B6AE" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19145b6e6e745c95b8f6dfe7fcb4cf8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0c70a35-bdec-4b82-a48e-fcb724eddf79" xmlns:ns4="43483a0c-d32e-43f3-ad27-4911fbdf68f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6fa41959bc4d6692baad636c69a7f73f" ns3:_="" ns4:_="">
     <xsd:import namespace="c0c70a35-bdec-4b82-a48e-fcb724eddf79"/>
@@ -5125,15 +6400,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5143,6 +6409,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A7C7F8C-40A2-4DC2-9533-5613D7DF82FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20E42477-D575-4A97-9FB8-D212EFAF9FE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5157,14 +6431,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A7C7F8C-40A2-4DC2-9533-5613D7DF82FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
